--- a/sheets/대금율보/검수/외로운 양치기.xlsx
+++ b/sheets/대금율보/검수/외로운 양치기.xlsx
@@ -4724,11 +4724,7 @@
         </is>
       </c>
       <c r="M5" s="23"/>
-      <c r="N5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="24"/>
       <c r="O5" s="25"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="23"/>
@@ -4909,11 +4905,7 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B9" s="24"/>
       <c r="C9" s="25"/>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
@@ -5157,11 +5149,7 @@
         </is>
       </c>
       <c r="O13" s="23"/>
-      <c r="P13" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P13" s="24"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
@@ -5361,11 +5349,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D17" s="24"/>
       <c r="E17" s="25"/>
       <c r="F17" s="21"/>
       <c r="G17" s="23"/>
@@ -5380,11 +5364,7 @@
       <c r="K17" s="23"/>
       <c r="L17" s="21"/>
       <c r="M17" s="23"/>
-      <c r="N17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N17" s="24"/>
       <c r="O17" s="25"/>
       <c r="P17" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/외로운 양치기.xlsx
+++ b/sheets/대금율보/검수/외로운 양치기.xlsx
@@ -4534,32 +4534,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -4733,7 +4733,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="24"/>
       <c r="C9" s="25"/>
@@ -4946,7 +4946,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="24" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5345,7 +5345,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5378,7 +5378,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="24" t="inlineStr">
         <is>
@@ -5441,6 +5441,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>